--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_5.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02016699432178821</v>
+        <v>0.01430528217329816</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008417574008314306</v>
+        <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31815405</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31815405</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>22674414</v>
+        <v>4363453</v>
       </c>
       <c r="L2" t="n">
-        <v>12825692</v>
+        <v>2360177</v>
       </c>
       <c r="M2" t="n">
-        <v>3189508</v>
+        <v>554212</v>
       </c>
       <c r="N2" t="n">
-        <v>170921</v>
+        <v>22997</v>
       </c>
       <c r="O2" t="n">
-        <v>1923476</v>
+        <v>335917</v>
       </c>
       <c r="P2" t="n">
-        <v>777090</v>
+        <v>134806</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999988853931427</v>
+        <v>0.9999897480010986</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8868376016616821</v>
+        <v>0.8528417348861694</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7742836475372314</v>
+        <v>0.708832323551178</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7078070044517517</v>
+        <v>0.6360813975334167</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4386301338672638</v>
+        <v>0.2364049404859543</v>
       </c>
       <c r="V2" t="n">
-        <v>0.763992965221405</v>
+        <v>0.6924653053283691</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8316317200660706</v>
+        <v>0.7937001585960388</v>
       </c>
       <c r="X2" t="n">
-        <v>31815405</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31815405</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24301454</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14980553</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4010938</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295947</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2297505</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900314</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565000534057617</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113458395004272</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579315543174744</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619642376899719</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019256830215454</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314380288124084</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.004937139222723819</v>
+        <v>0.003399331293332228</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00201677850552652</v>
+        <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>22674414</v>
+        <v>4363453</v>
       </c>
       <c r="E3" t="n">
-        <v>2620167</v>
+        <v>674087</v>
       </c>
       <c r="F3" t="n">
-        <v>66863</v>
+        <v>12184</v>
       </c>
       <c r="G3" t="n">
-        <v>12354</v>
+        <v>1391</v>
       </c>
       <c r="H3" t="n">
-        <v>3430</v>
+        <v>741</v>
       </c>
       <c r="I3" t="n">
-        <v>205</v>
+        <v>24</v>
       </c>
       <c r="J3" t="n">
-        <v>50480240</v>
+        <v>10069555</v>
       </c>
       <c r="K3" t="n">
-        <v>54025250</v>
+        <v>10611200</v>
       </c>
       <c r="L3" t="n">
-        <v>62094460</v>
+        <v>12156408</v>
       </c>
       <c r="M3" t="n">
-        <v>76301327</v>
+        <v>15163803</v>
       </c>
       <c r="N3" t="n">
-        <v>81629884</v>
+        <v>16252300</v>
       </c>
       <c r="O3" t="n">
-        <v>79153433</v>
+        <v>15757108</v>
       </c>
       <c r="P3" t="n">
-        <v>81171912</v>
+        <v>16187568</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8934868574142456</v>
+        <v>0.863727867603302</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7790786623954773</v>
+        <v>0.7173572182655334</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6818104386329651</v>
+        <v>0.5926653146743774</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3820599317550659</v>
+        <v>0.2571824789047241</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7547835111618042</v>
+        <v>0.6590406894683838</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8038069605827332</v>
+        <v>0.69705730676651</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24301454</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>998327</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>43049</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34241</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50480595</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55813367</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64376076</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76953814</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81697506</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79497791</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81262967</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957600474357605</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099726676940918</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574048280715942</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615306735038757</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015547633171082</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312674403190613</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05375843153023448</v>
+        <v>0.0408529026260002</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03186790886167197</v>
+        <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2739045</v>
+        <v>713822</v>
       </c>
       <c r="E4" t="n">
-        <v>12825692</v>
+        <v>2360177</v>
       </c>
       <c r="F4" t="n">
-        <v>796872</v>
+        <v>189509</v>
       </c>
       <c r="G4" t="n">
-        <v>32807</v>
+        <v>9386</v>
       </c>
       <c r="H4" t="n">
-        <v>62444</v>
+        <v>15890</v>
       </c>
       <c r="I4" t="n">
-        <v>5764</v>
+        <v>1316</v>
       </c>
       <c r="J4" t="n">
-        <v>355</v>
+        <v>65</v>
       </c>
       <c r="K4" t="n">
-        <v>2893304</v>
+        <v>752916</v>
       </c>
       <c r="L4" t="n">
-        <v>3738899</v>
+        <v>969492</v>
       </c>
       <c r="M4" t="n">
-        <v>1316675</v>
+        <v>317079</v>
       </c>
       <c r="N4" t="n">
-        <v>218749</v>
+        <v>74281</v>
       </c>
       <c r="O4" t="n">
-        <v>594186</v>
+        <v>149186</v>
       </c>
       <c r="P4" t="n">
-        <v>157326</v>
+        <v>35039</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999944567680359</v>
+        <v>0.9999948740005493</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8901498317718506</v>
+        <v>0.8582502603530884</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7766737341880798</v>
+        <v>0.7130692601203918</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6945655345916748</v>
+        <v>0.613606333732605</v>
       </c>
       <c r="U4" t="n">
-        <v>0.408395379781723</v>
+        <v>0.2463563829660416</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7593603730201721</v>
+        <v>0.6753396987915039</v>
       </c>
       <c r="W4" t="n">
-        <v>0.817482590675354</v>
+        <v>0.742246150970459</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1031917</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14980553</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>416440</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27651</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5740</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1105187</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1457283</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>664188</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>151127</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249828</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66271</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570499658584595</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106587171554565</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576681017875671</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617473959922791</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017401933670044</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313527345657349</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>98610</v>
+        <v>25497</v>
       </c>
       <c r="E5" t="n">
-        <v>966995</v>
+        <v>252024</v>
       </c>
       <c r="F5" t="n">
-        <v>3189508</v>
+        <v>554212</v>
       </c>
       <c r="G5" t="n">
-        <v>86098</v>
+        <v>26411</v>
       </c>
       <c r="H5" t="n">
-        <v>311551</v>
+        <v>70433</v>
       </c>
       <c r="I5" t="n">
-        <v>25227</v>
+        <v>6538</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2703032</v>
+        <v>688431</v>
       </c>
       <c r="L5" t="n">
-        <v>3636949</v>
+        <v>929923</v>
       </c>
       <c r="M5" t="n">
-        <v>1488490</v>
+        <v>380906</v>
       </c>
       <c r="N5" t="n">
-        <v>276446</v>
+        <v>66422</v>
       </c>
       <c r="O5" t="n">
-        <v>624905</v>
+        <v>173789</v>
       </c>
       <c r="P5" t="n">
-        <v>189672</v>
+        <v>58587</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999957084655762</v>
+        <v>0.9999960660934448</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9319974780082703</v>
+        <v>0.9121986627578735</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9103741645812988</v>
+        <v>0.884294867515564</v>
       </c>
       <c r="T5" t="n">
-        <v>0.965913712978363</v>
+        <v>0.9574814438819885</v>
       </c>
       <c r="U5" t="n">
-        <v>0.99398273229599</v>
+        <v>0.9914289116859436</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9851865172386169</v>
+        <v>0.9803255796432495</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9957835078239441</v>
+        <v>0.994296669960022</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40436</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>427565</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4010938</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49917</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145977</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1075992</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1482088</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>667060</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151420</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250876</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66448</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734959006309509</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642829298973083</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838236570358276</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963236451148987</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939157962799072</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983872771263123</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>53927</v>
+        <v>13270</v>
       </c>
       <c r="E6" t="n">
-        <v>73411</v>
+        <v>19667</v>
       </c>
       <c r="F6" t="n">
-        <v>92606</v>
+        <v>21657</v>
       </c>
       <c r="G6" t="n">
-        <v>170921</v>
+        <v>22997</v>
       </c>
       <c r="H6" t="n">
-        <v>50975</v>
+        <v>10696</v>
       </c>
       <c r="I6" t="n">
-        <v>5471</v>
+        <v>1122</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32554</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26929</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54569</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295947</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34963</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>1601</v>
+        <v>295</v>
       </c>
       <c r="E7" t="n">
-        <v>73975</v>
+        <v>22582</v>
       </c>
       <c r="F7" t="n">
-        <v>346359</v>
+        <v>89629</v>
       </c>
       <c r="G7" t="n">
-        <v>82223</v>
+        <v>35221</v>
       </c>
       <c r="H7" t="n">
-        <v>1923476</v>
+        <v>335917</v>
       </c>
       <c r="I7" t="n">
-        <v>120659</v>
+        <v>26039</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4057</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148478</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37990</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2297505</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60211</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>4351</v>
+        <v>1132</v>
       </c>
       <c r="F8" t="n">
-        <v>13975</v>
+        <v>4100</v>
       </c>
       <c r="G8" t="n">
-        <v>5267</v>
+        <v>1872</v>
       </c>
       <c r="H8" t="n">
-        <v>165786</v>
+        <v>51426</v>
       </c>
       <c r="I8" t="n">
-        <v>777090</v>
+        <v>134806</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1652</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1328</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62923</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900314</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
